--- a/sheets/대금율보/검수/내가 바보야.xlsx
+++ b/sheets/대금율보/검수/내가 바보야.xlsx
@@ -5283,8 +5283,7 @@
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-潕潕
-‹</t>
+潕潕</t>
         </is>
       </c>
       <c r="G3" s="22" t="inlineStr">
@@ -5341,8 +5340,7 @@
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潕
-–湳
-‹</t>
+–湳</t>
         </is>
       </c>
       <c r="G4" s="25" t="inlineStr">
@@ -5353,7 +5351,6 @@
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–太
-‹
 太</t>
         </is>
       </c>
@@ -5365,7 +5362,6 @@
       <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰
-‹
 浹汰</t>
         </is>
       </c>
@@ -5437,8 +5433,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南
-‹</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C6" s="27"/>
@@ -5754,7 +5749,6 @@
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢
-‹
 潢</t>
         </is>
       </c>
@@ -5766,7 +5760,6 @@
       <c r="J12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
-‹
 潕</t>
         </is>
       </c>
@@ -5926,8 +5919,7 @@
       </c>
       <c r="J15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K15" s="22" t="inlineStr">
@@ -6021,8 +6013,7 @@
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰浹
-汰浹
-‹</t>
+汰浹</t>
         </is>
       </c>
       <c r="E18" s="27"/>
@@ -6135,7 +6126,6 @@
       <c r="J20" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
-‹
 淋</t>
         </is>
       </c>
@@ -6158,8 +6148,7 @@
       <c r="C21" s="25"/>
       <c r="D21" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">汏
-‹</t>
+          <t xml:space="preserve">汏</t>
         </is>
       </c>
       <c r="E21" s="26"/>
@@ -6275,8 +6264,7 @@
       <c r="J23" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-無南
-‹</t>
+無南</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -6310,7 +6298,6 @@
       <c r="J24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林
-‹
 南無</t>
         </is>
       </c>
@@ -6322,8 +6309,7 @@
       <c r="L24" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">浹汰
-浹湳
-‹</t>
+浹湳</t>
         </is>
       </c>
       <c r="M24" s="25"/>

--- a/sheets/대금율보/검수/내가 바보야.xlsx
+++ b/sheets/대금율보/검수/내가 바보야.xlsx
@@ -5230,24 +5230,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="93.02" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="69.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="69.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="69.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="69.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="M6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="69.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="M7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="69.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="69.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="M9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="69.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
       </c>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="69.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="22"/>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="M11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="69.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="69.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="69.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="M14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="69.36" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="M15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="69.36" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="25"/>
@@ -5968,7 +5968,7 @@
       <c r="L16" s="21"/>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="69.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="25"/>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="M17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="69.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="27"/>
@@ -6049,7 +6049,7 @@
       </c>
       <c r="M18" s="27"/>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="69.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21"/>
       <c r="C19" s="22"/>
@@ -6094,7 +6094,7 @@
       </c>
       <c r="M19" s="22"/>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="69.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -6142,7 +6142,7 @@
       </c>
       <c r="M20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="69.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -6187,7 +6187,7 @@
       </c>
       <c r="M21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="69.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21"/>
       <c r="C22" s="27"/>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="M22" s="27"/>
     </row>
-    <row r="23" ht="56" customHeight="1">
+    <row r="23" ht="69.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21"/>
       <c r="C23" s="22"/>
@@ -6280,7 +6280,7 @@
       </c>
       <c r="M23" s="22"/>
     </row>
-    <row r="24" ht="56" customHeight="1">
+    <row r="24" ht="69.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="25"/>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M24" s="25"/>
     </row>
-    <row r="25" ht="56" customHeight="1">
+    <row r="25" ht="69.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="25"/>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="M25" s="25"/>
     </row>
-    <row r="26" ht="56" customHeight="1">
+    <row r="26" ht="69.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="27"/>
@@ -6398,6 +6398,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="52"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="43"/>
 </worksheet>
 </file>